--- a/KURIKULUM2026_REVISI/036_DEV_REPORT_DAN_LOG_RESTRUKTURISASI_KODE_PEMINATAN.xlsx
+++ b/KURIKULUM2026_REVISI/036_DEV_REPORT_DAN_LOG_RESTRUKTURISASI_KODE_PEMINATAN.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>`STI-413` Machine Learning, `STI-624` Integrasi AI</t>
+          <t>`STI-413` Machine Learning, `STI-726` Integrasi AI</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>`STI-626` Deep Learning, `STI-521` IoT</t>
+          <t>`STI-726` Deep Learning, `STI-521` IoT</t>
         </is>
       </c>
     </row>
